--- a/Project_Schedule_Lab_v0.1.0/Project_Schedule_Lab_v0.1.0/examples/validation_small.xlsx
+++ b/Project_Schedule_Lab_v0.1.0/Project_Schedule_Lab_v0.1.0/examples/validation_small.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.2.0</t>
+          <t>0.2.1</t>
         </is>
       </c>
     </row>
